--- a/HealthClick_Automation_Bug_Report.xlsx
+++ b/HealthClick_Automation_Bug_Report.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.85546875" customWidth="1" min="1" max="1"/>
@@ -7659,6 +7659,5414 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BUG-139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BUG-140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Organizations page should open</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Organizations page was not open</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:17:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BUG-141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Billings page should open</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Billings page was not open</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:17:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BUG-142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>EHR template page should open</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>EHR template page was not open</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BUG-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Departments page should open</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Departments page was not open</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BUG-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>General info should open</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>General info was not open</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:18:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BUG-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Terms page should open</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Terms page was not open</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BUG-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Privacy page should open</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Privacy page was not open</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BUG-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ADMIN SETTINGS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Admin settings should open</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Admin settings was not open</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BUG-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>User should logout</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>User should logout was not successful</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>BUG-149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Dashboard page should be displayed</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Dashboard page was not displayed</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>BUG-150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections should be visible</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections was not visible</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BUG-151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Verify Sales date picker inputs are present</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Verify Sales date picker inputs are present</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>From and To date inputs should be present</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>From and To date inputs should be present was not successful</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BUG-152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Verify Sales date input manual entry</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Verify Sales date input manual entry</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Sales date fields should accept manual input</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Sales date fields should accept manual input was not successful</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>BUG-153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Verify Create Organization button click and page load</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Verify Create Organization button click and page load</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Create Organization page should open</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Create Organization page was not open</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BUG-154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BUG-155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:19:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BUG-156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Open Create Organization page</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Open Create Organization page</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Create Organization page should open</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Create Organization page was not open</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:20:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BUG-157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Create Organization</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Enter valid organization data</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Enter valid organization data</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>All mandatory fields should be filled</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>All mandatory fields were not filled</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:20:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BUG-158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Create Organization</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Save organization</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Save organization</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Organization should be created successfully</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Organization was not created successfully</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BUG-159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:21:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BUG-160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BUG-161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>All Organizations page should open</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>All Organizations page was not open</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:21:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BUG-162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Open first organization record</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Open first organization record</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Organization details page should open</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Organization details page was not open</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:21:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BUG-163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Fill Details tab and proceed</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Fill Details tab and proceed</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Details saved</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Details was not saved</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BUG-164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Add 3rd branch and proceed</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Add 3rd branch and proceed</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Branch saved</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Branch was not saved</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>BUG-165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Departments</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Allocate departments and proceed</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Allocate departments and proceed</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Departments saved</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Departments was not saved</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BUG-166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Review package and finish</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Review package and finish</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Package completed</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Package was not completed</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BUG-167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>User logged out</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>User logged out was not successful</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>BUG-168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:22:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>BUG-169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>All Billings page should open</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>All Billings page was not open</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BUG-170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Verify All Billings page loaded</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Verify All Billings page loaded</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Billing table should be visible</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Billing table was not visible</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:23:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>BUG-171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Verify billing records</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Verify billing records</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Billing records should be present</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Billing records should be present was not successful</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:23:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>BUG-172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Search billing</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Search billing</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Filtered results should appear</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Filtered results should appear was not successful</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:23:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>BUG-173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:23:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>BUG-174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:24:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BUG-175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>EHR Template page should open</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>EHR Template page was not open</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:24:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>BUG-176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Select Pediatrician department</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Select Pediatrician department</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Pediatrician department should be selected</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Pediatrician department should be selected was not successful</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:24:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>BUG-177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Vitals</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Open Vitals tab</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Open Vitals tab</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Vitals tab should open</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Vitals tab was not open</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:24:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BUG-178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Vitals</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Vitals Create popup</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Vitals Create popup</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Create popup should open</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Create popup was not open</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:25:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BUG-179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Vitals</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Vitals Search</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Vitals Search</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Search should work</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Search should work was not successful</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:25:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BUG-180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Vitals</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Vitals Status change</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Vitals Status change</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Status should change</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Status should change was not successful</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:25:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BUG-181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Open Complaint tab</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Open Complaint tab</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Complaint tab should open</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Complaint tab was not open</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:25:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BUG-182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Complaint Create</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Complaint Create</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:26:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BUG-183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Complaint Search</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Complaint Search</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:26:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BUG-184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Complaint Status change</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Complaint Status change</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:26:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BUG-185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Open History tab</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Open History tab</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>History tab should open</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>History tab was not open</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:26:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>BUG-186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>History Create</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>History Create</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:26:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BUG-187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>History Search</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>History Search</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BUG-188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>History Status change</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>History Status change</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>BUG-189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Open Diagnosis tab</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Open Diagnosis tab</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Diagnosis tab should open</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Diagnosis tab was not open</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BUG-190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Diagnosis Create</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Diagnosis Create</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>BUG-191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Diagnosis Search</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Diagnosis Search</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BUG-192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Diagnosis Status change</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Diagnosis Status change</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BUG-193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Advice</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Open Advice tab</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Open Advice tab</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Advice tab should open</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Advice tab was not open</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BUG-194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Advice</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Advice Create</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Advice Create</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BUG-195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Advice</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Advice Search</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Advice Search</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BUG-196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Advice</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Advice Status change</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Advice Status change</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BUG-197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Open Treatment tab</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Open Treatment tab</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Treatment tab should open</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Treatment tab was not open</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BUG-198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Treatment Create</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Treatment Create</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BUG-199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Treatment Search</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Treatment Search</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BUG-200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Treatment Status change</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Treatment Status change</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BUG-201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ProgressNote</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Open ProgressNote tab</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Open ProgressNote tab</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ProgressNote tab should open</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>ProgressNote tab was not open</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BUG-202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ProgressNote</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ProgressNote Create</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ProgressNote Create</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Create popup should open and save data</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Create popup was not open and save data</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BUG-203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ProgressNote</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ProgressNote Search</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ProgressNote Search</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BUG-204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ProgressNote</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ProgressNote Status change</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ProgressNote Status change</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Status should change successfully</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Status should change successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BUG-205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Open Medicine Template</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Open Medicine Template</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Medicine template page should open</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Medicine template page was not open</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BUG-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Create Medicine Template</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Create Medicine Template</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Medicine template should be created</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Medicine template should be was not created</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BUG-207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Verify Medicine Search</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Verify Medicine Search</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Search should work</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Search should work was not successful</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BUG-208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Medicine</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Verify Medicine Status Change</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Verify Medicine Status Change</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Status should change</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Status should change was not successful</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BUG-209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Prescription</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Open Prescription Template</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Open Prescription Template</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Prescription template page should open</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Prescription template page was not open</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BUG-210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Prescription</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Create Prescription Template</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Create Prescription Template</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Prescription template should be created</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Prescription template should be was not created</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BUG-211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:27:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BUG-212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>BUG-213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DEPARTMENTS &amp; TESTS</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Open Departments &amp; Tests</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Open Departments &amp; Tests</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Page should open</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Page was not open</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BUG-214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ALL DEPARTMENTS</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Open All Departments tab</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Open All Departments tab</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>All Departments should be visible</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>All Departments was not visible</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>BUG-215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ALL DEPARTMENTS</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Search department</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Search department</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Search should filter records</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Search should filter records was not successful</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BUG-216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ALL DEPARTMENTS</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Download CSV</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Download CSV</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>CSV should download</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>CSV should download was not successful</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BUG-217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ALL DEPARTMENTS</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Download PDF</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Download PDF</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>PDF should download</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>PDF should download was not successful</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>BUG-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Open All Tests tab</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Open All Tests tab</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>All Tests should be visible</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>All Tests was not visible</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>BUG-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Search test</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Search test</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Search should filter tests</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Search should filter tests was not successful</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BUG-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Download CSV</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Download CSV</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>CSV should download</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>CSV should download was not successful</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BUG-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Download</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Download PDF</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Download PDF</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>PDF should download</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>PDF should download was not successful</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BUG-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Open Add New Test popup</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Open Add New Test popup</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Create Test popup should open</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Create Test popup was not open</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BUG-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Popup</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Close Create Test popup</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Close Create Test popup</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Popup should close</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Popup should close was not successful</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BUG-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ALL TESTS</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Open Edit Test</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Open Edit Test</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Edit popup should open</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Edit popup was not open</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BUG-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>User should logout</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>User should logout was not successful</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BUG-226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BUG-227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>General Info</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>General Info page should open</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>General Info page was not open</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BUG-228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>General Info</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Append General Info data</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Append General Info data</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Data should be appended</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Data should be appended was not successful</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BUG-229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>General Info</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Save General Info</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Save General Info</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Data should be saved</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Data should be was not saved</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BUG-230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>General Info</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Clear General Info</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Clear General Info</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Content should be cleared</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Content should be cleared was not successful</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>BUG-231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Terms page should open</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Terms page was not open</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>BUG-232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Append Terms data</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Append Terms data</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Data should be appended</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Data should be appended was not successful</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>BUG-233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Save Terms data</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Save Terms data</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Data should be saved</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Data should be was not saved</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>BUG-234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Clear Terms data</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Clear Terms data</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Content should be cleared</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Content should be cleared was not successful</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>BUG-235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Privacy page should open</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Privacy page was not open</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BUG-236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Append Privacy Policy data</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Append Privacy Policy data</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Data should be appended</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Data should be appended was not successful</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>BUG-237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Save Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Save Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Data should be saved</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Data should be was not saved</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>BUG-238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Clear Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Clear Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Content should be cleared</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Content should be cleared was not successful</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>BUG-239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BUG-240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>BUG-241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ADMIN SETTINGS</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Admin Settings should open</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Admin Settings was not open</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>BUG-242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>User should be logged out successfully</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>User should be logged out successfully was not successful</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2026-04-12 01:28:56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HealthClick_Automation_Bug_Report.xlsx
+++ b/HealthClick_Automation_Bug_Report.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.85546875" customWidth="1" min="1" max="1"/>
@@ -13067,6 +13067,1670 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BUG-243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:02:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>BUG-244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Organizations page should open</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Organizations page was not open</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:02:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>BUG-245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Billings page should open</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Billings page was not open</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>BUG-246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>EHR template page should open</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>EHR template page was not open</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>BUG-247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Departments page should open</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Departments page was not open</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:03:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BUG-248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>General info should open</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>General info was not open</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:03:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>BUG-249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Terms page should open</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Terms page was not open</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:03:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>BUG-250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Privacy page should open</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Privacy page was not open</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BUG-251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ADMIN SETTINGS</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Admin settings should open</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Admin settings was not open</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:04:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>BUG-252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>User should logout</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>User should logout was not successful</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:04:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BUG-253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Dashboard page should be displayed</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Dashboard page was not displayed</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>BUG-254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections should be visible</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections was not visible</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:05:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BUG-255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>BUG-256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>BUG-257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Open Create Organization page</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Open Create Organization page</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Create Organization page should open</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Create Organization page was not open</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:06:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>BUG-258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Create Organization</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Enter valid organization data</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Enter valid organization data</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>All mandatory fields should be filled</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>All mandatory fields were not filled</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:06:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BUG-259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>CREATE_ORG</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Create Organization</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Save organization</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Save organization</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Organization should be created successfully</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Organization was not created successfully</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:07:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BUG-260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:07:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>BUG-261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BUG-262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>All Organizations page should open</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>All Organizations page was not open</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:07:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BUG-263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Open first organization record</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Open first organization record</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Organization details page should open</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Organization details page was not open</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BUG-264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Fill Details tab and proceed</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Fill Details tab and proceed</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Details saved</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Details was not saved</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BUG-265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Add 3rd branch and proceed</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Add 3rd branch and proceed</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Branch saved</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Branch was not saved</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BUG-266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Departments</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Allocate departments and proceed</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Allocate departments and proceed</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Departments saved</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Departments was not saved</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:08:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BUG-267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ALL_ORG</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Review package and finish</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Review package and finish</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Package completed</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Package was not completed</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BUG-268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>User logged out</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>User logged out was not successful</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BUG-269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Dashboard should be visible</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Dashboard was not visible</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>BUG-270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>All Billings page should open</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>All Billings page was not open</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BUG-271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Verify All Billings page loaded</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Verify All Billings page loaded</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Billing table should be visible</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Billing table was not visible</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BUG-272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Verify billing records</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Verify billing records</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Billing records should be present</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Billing records should be present was not successful</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>BUG-273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ALL_BILLINGS</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Search billing</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Search billing</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Filtered results should appear</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Filtered results should appear was not successful</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>BUG-274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:09:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HealthClick_Automation_Bug_Report.xlsx
+++ b/HealthClick_Automation_Bug_Report.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J275"/>
+  <dimension ref="A1:J294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.85546875" customWidth="1" min="1" max="1"/>
@@ -14731,6 +14731,994 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>BUG-275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>BUG-276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>EHR Template page should open</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>EHR Template page was not open</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>BUG-277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>EHR</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Select Pediatrician department</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Select Pediatrician department</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Pediatrician department should be selected</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Pediatrician department should be selected was not successful</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:10:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BUG-278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Verify dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Dashboard should load</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Dashboard should load was not successful</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:13:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>BUG-279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Open All Organizations</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Organizations page should open</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Organizations page was not open</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>BUG-280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Open All Billings</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Billings page should open</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Billings page was not open</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>BUG-281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Open EHR Template</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>EHR template page should open</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>EHR template page was not open</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>BUG-282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Open Departments</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Departments page should open</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Departments page was not open</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:14:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>BUG-283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Open General Info</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>General info should open</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>General info was not open</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BUG-284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Open Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Terms page should open</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Terms page was not open</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BUG-285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>INFO &amp; POLICIES</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Open Privacy Policy</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Privacy page should open</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Privacy page was not open</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BUG-286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ADMIN SETTINGS</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Open Admin Settings</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Admin settings should open</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Admin settings was not open</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>BUG-287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>User should logout</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>User should logout was not successful</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BUG-288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Verify dashboard page loads</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Dashboard page should be displayed</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Dashboard page was not displayed</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BUG-289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Verify main dashboard sections visibility</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections should be visible</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Summary, Sales, and Customers sections was not visible</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BUG-290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Verify Sales date picker inputs are present</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Verify Sales date picker inputs are present</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>From and To date inputs should be present</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>From and To date inputs should be present was not successful</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>BUG-291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Verify Sales date input manual entry</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Verify Sales date input manual entry</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Sales date fields should accept manual input</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Sales date fields should accept manual input was not successful</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>BUG-292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Verify Create Organization button click and page load</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Verify Create Organization button click and page load</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Create Organization page should open</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Create Organization page was not open</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BUG-293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>LOGOUT</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Logout from application</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>User should logout successfully</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>User did not logout successfully</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>2026-04-12 02:15:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
